--- a/dados/123.xlsx
+++ b/dados/123.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="98">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -75,13 +75,16 @@
     <t>Rafael Nicolucci de Oliveira</t>
   </si>
   <si>
-    <t>TESTEMUNHA DE JEOVA</t>
+    <t>UNIVERSAL</t>
   </si>
   <si>
     <t>Nathália Machado Vieira de Oliveira</t>
   </si>
   <si>
     <t>Théo Vieira de Oliveira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL </t>
   </si>
   <si>
     <t>Lucas Medeiros</t>
@@ -983,7 +986,7 @@
         <v>1.5998329292E10</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>11</v>
@@ -1004,7 +1007,7 @@
         <v>45988.88085091436</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="8">
         <v>31.0</v>
@@ -1013,7 +1016,7 @@
         <v>1.5997383252E10</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>11</v>
@@ -1034,7 +1037,7 @@
         <v>45989.35557366898</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="14">
         <v>13.0</v>
@@ -1043,7 +1046,7 @@
         <v>1.5998073905E10</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>11</v>
@@ -1065,7 +1068,7 @@
         <v>45991.72189862268</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="8">
         <v>36.0</v>
@@ -1095,7 +1098,7 @@
         <v>45992.35183858796</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="14">
         <v>33.0</v>
@@ -1125,7 +1128,7 @@
         <v>46008.748270578704</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="8">
         <v>13.0</v>
@@ -1155,7 +1158,7 @@
         <v>46015.51542157408</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="8">
         <v>16.0</v>
@@ -1185,7 +1188,7 @@
         <v>46026.851575520835</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="11">
         <v>14.0</v>
@@ -1197,7 +1200,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>12</v>
@@ -1216,7 +1219,7 @@
         <v>46034.93480728009</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="14">
         <v>16.0</v>
@@ -1246,7 +1249,7 @@
         <v>46041.32586482639</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="8">
         <v>19.0</v>
@@ -1276,7 +1279,7 @@
         <v>46044.81511322917</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" s="8">
         <v>15.0</v>
@@ -1306,7 +1309,7 @@
         <v>46044.81827189815</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="8">
         <v>12.0</v>
@@ -1336,7 +1339,7 @@
         <v>46046.64678542824</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="14">
         <v>12.0</v>
@@ -1366,7 +1369,7 @@
         <v>46064.82448491898</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="8">
         <v>29.0</v>
@@ -1396,7 +1399,7 @@
         <v>46068.70991171296</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C22" s="14">
         <v>52.0</v>
@@ -1426,7 +1429,7 @@
         <v>46069.48487325231</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="14">
         <v>53.0</v>
@@ -1435,7 +1438,7 @@
         <v>1.9992764207E10</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>11</v>
@@ -1456,7 +1459,7 @@
         <v>46069.485649780094</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" s="14">
         <v>48.0</v>
@@ -1465,7 +1468,7 @@
         <v>1.9991540189E10</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>11</v>
@@ -1486,7 +1489,7 @@
         <v>46070.4851490625</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25" s="14">
         <v>31.0</v>
@@ -1516,7 +1519,7 @@
         <v>46070.48898782408</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" s="14">
         <v>27.0</v>
@@ -1546,7 +1549,7 @@
         <v>46070.49287108796</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C27" s="8">
         <v>40.0</v>
@@ -1555,7 +1558,7 @@
         <v>1.9981865798E10</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>11</v>
@@ -1576,7 +1579,7 @@
         <v>46070.49458613426</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C28" s="8">
         <v>11.0</v>
@@ -1585,7 +1588,7 @@
         <v>1.9981865798E10</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>11</v>
@@ -1606,7 +1609,7 @@
         <v>46070.49686550926</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" s="8">
         <v>8.0</v>
@@ -1615,7 +1618,7 @@
         <v>1.9981865798E10</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>11</v>
@@ -1636,7 +1639,7 @@
         <v>46070.49971831018</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C30" s="8">
         <v>33.0</v>
@@ -1645,7 +1648,7 @@
         <v>1.9981865797E10</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>11</v>
@@ -1666,7 +1669,7 @@
         <v>46070.51280806713</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" s="8">
         <v>30.0</v>
@@ -1696,7 +1699,7 @@
         <v>46074.65327711806</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C32" s="14">
         <v>45.0</v>
@@ -1726,7 +1729,7 @@
         <v>46074.95314136574</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C33" s="14">
         <v>33.0</v>
@@ -1738,7 +1741,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>15</v>
@@ -1756,7 +1759,7 @@
         <v>46075.539279652774</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" s="8">
         <v>12.0</v>
@@ -1768,10 +1771,10 @@
         <v>10</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H34" s="6">
         <v>0.0</v>
@@ -1786,7 +1789,7 @@
         <v>46075.75095246528</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C35" s="14">
         <v>23.0</v>
@@ -1795,10 +1798,10 @@
         <v>1.998259793E10</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>15</v>
@@ -1816,7 +1819,7 @@
         <v>46075.75320802083</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C36" s="14">
         <v>20.0</v>
@@ -1825,10 +1828,10 @@
         <v>1.9981308647E10</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>15</v>
@@ -1846,7 +1849,7 @@
         <v>46078.29362975694</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C37" s="14">
         <v>34.0</v>
@@ -1855,10 +1858,10 @@
         <v>1.5996039339E10</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G37" s="14" t="s">
         <v>15</v>
@@ -1876,7 +1879,7 @@
         <v>46078.95354269676</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C38" s="8">
         <v>36.0</v>
@@ -1888,7 +1891,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>15</v>
@@ -1906,7 +1909,7 @@
         <v>46078.95630763889</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C39" s="8">
         <v>38.0</v>
@@ -1936,7 +1939,7 @@
         <v>46079.45182004629</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C40" s="8">
         <v>30.0</v>
@@ -1948,10 +1951,10 @@
         <v>10</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H40" s="6">
         <v>0.0</v>
@@ -1965,7 +1968,7 @@
         <v>46079.45345880787</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C41" s="8">
         <v>34.0</v>
@@ -1977,10 +1980,10 @@
         <v>10</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H41" s="6">
         <v>0.0</v>
@@ -1994,7 +1997,7 @@
         <v>46082.54593087963</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C42" s="8">
         <v>34.0</v>
@@ -2006,10 +2009,10 @@
         <v>10</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H42" s="6">
         <v>0.0</v>
@@ -2023,7 +2026,7 @@
         <v>46082.54697430556</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C43" s="8">
         <v>37.0</v>
@@ -2035,10 +2038,10 @@
         <v>10</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H43" s="6">
         <v>0.0</v>
@@ -2052,7 +2055,7 @@
         <v>46082.82621666667</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C44" s="8">
         <v>10.0</v>
@@ -2064,10 +2067,10 @@
         <v>10</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H44" s="6">
         <v>0.0</v>
@@ -2081,7 +2084,7 @@
         <v>46082.82685563657</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C45" s="8">
         <v>7.0</v>
@@ -2093,10 +2096,10 @@
         <v>10</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H45" s="6">
         <v>0.0</v>
@@ -2110,7 +2113,7 @@
         <v>46082.866330081015</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C46" s="8">
         <v>19.0</v>
@@ -2122,7 +2125,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>15</v>
@@ -2140,7 +2143,7 @@
         <v>46083.51295694444</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="14">
         <v>19.0</v>
@@ -2152,7 +2155,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>15</v>
@@ -2170,7 +2173,7 @@
         <v>46084.47416711805</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="11">
         <v>12.0</v>
@@ -2179,10 +2182,10 @@
         <v>1.5981381818E10</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G48" s="11" t="s">
         <v>15</v>
@@ -2200,7 +2203,7 @@
         <v>46088.44795631945</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C49" s="14">
         <v>61.0</v>
@@ -2209,10 +2212,10 @@
         <v>1.199997487E10</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G49" s="14" t="s">
         <v>15</v>
@@ -2230,7 +2233,7 @@
         <v>46088.44901105324</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C50" s="14">
         <v>64.0</v>
@@ -2239,10 +2242,10 @@
         <v>1.199997487E10</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="14" t="s">
         <v>15</v>
@@ -2260,7 +2263,7 @@
         <v>46091.45505960648</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C51" s="8">
         <v>37.0</v>
@@ -2269,13 +2272,13 @@
         <v>1.5981647628E10</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H51" s="6">
         <v>0.0</v>
@@ -2290,7 +2293,7 @@
         <v>46091.457525555554</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C52" s="8">
         <v>30.0</v>
@@ -2299,13 +2302,13 @@
         <v>1.599675357E10</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H52" s="6">
         <v>0.0</v>
@@ -2320,7 +2323,7 @@
         <v>46091.90208714121</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C53" s="8">
         <v>23.0</v>
@@ -2329,10 +2332,10 @@
         <v>1.9982012292E10</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>15</v>
@@ -2350,7 +2353,7 @@
         <v>46093.27018577546</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C54" s="14">
         <v>58.0</v>
@@ -2359,10 +2362,10 @@
         <v>1.5991416337E10</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G54" s="14" t="s">
         <v>15</v>
@@ -2380,7 +2383,7 @@
         <v>46093.27149944444</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C55" s="14">
         <v>58.0</v>
@@ -2389,10 +2392,10 @@
         <v>1.5988081595E10</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G55" s="14" t="s">
         <v>15</v>
@@ -2410,7 +2413,7 @@
         <v>46093.42218518518</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C56" s="8">
         <v>35.0</v>
@@ -2422,10 +2425,10 @@
         <v>10</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H56" s="6">
         <v>0.0</v>
@@ -2440,7 +2443,7 @@
         <v>46093.42287763889</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C57" s="8">
         <v>40.0</v>
@@ -2452,10 +2455,10 @@
         <v>10</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H57" s="6">
         <v>0.0</v>
@@ -2470,7 +2473,7 @@
         <v>46093.42378237269</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C58" s="8">
         <v>9.0</v>
@@ -2482,10 +2485,10 @@
         <v>10</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H58" s="6">
         <v>0.0</v>
@@ -2500,7 +2503,7 @@
         <v>46093.424697407405</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C59" s="8">
         <v>5.0</v>
@@ -2512,10 +2515,10 @@
         <v>10</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H59" s="6">
         <v>0.0</v>
@@ -2530,7 +2533,7 @@
         <v>46093.523896493054</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C60" s="8">
         <v>27.0</v>
@@ -2542,7 +2545,7 @@
         <v>10</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>15</v>
@@ -2560,7 +2563,7 @@
         <v>46093.70856616898</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C61" s="14">
         <v>19.0</v>
@@ -2572,7 +2575,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G61" s="14" t="s">
         <v>15</v>
@@ -2590,7 +2593,7 @@
         <v>46094.71026572917</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C62" s="8">
         <v>19.0</v>
@@ -2599,13 +2602,13 @@
         <v>1.1955200793E10</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H62" s="6">
         <v>0.0</v>
@@ -2620,7 +2623,7 @@
         <v>46095.34617701389</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C63" s="8">
         <v>37.0</v>
@@ -2629,13 +2632,13 @@
         <v>1.5997232525E10</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I63" s="21">
         <f t="shared" si="3"/>
@@ -2653,7 +2656,7 @@
     <row r="66">
       <c r="A66" s="24"/>
       <c r="B66" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C66" s="24"/>
       <c r="D66" s="24"/>
@@ -2671,7 +2674,7 @@
     <row r="67">
       <c r="A67" s="24"/>
       <c r="B67" s="25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C67" s="24"/>
       <c r="D67" s="24"/>
@@ -2692,7 +2695,7 @@
     </row>
     <row r="69">
       <c r="G69" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H69" s="22">
         <f t="shared" ref="H69:I69" si="5">SUM(H2:H67)</f>
@@ -2703,7 +2706,7 @@
         <v>6948</v>
       </c>
       <c r="J69" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70">
@@ -2712,7 +2715,7 @@
     </row>
     <row r="71">
       <c r="G71" s="28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H71" s="23">
         <f>300+100</f>
@@ -2730,7 +2733,7 @@
     </row>
     <row r="74">
       <c r="G74" s="28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H74" s="22">
         <f>H69+H71</f>

--- a/dados/123.xlsx
+++ b/dados/123.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="96">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Rafael Nicolucci de Oliveira</t>
+  </si>
+  <si>
+    <t>IPB - TESTE</t>
   </si>
   <si>
     <t>Nathália Machado Vieira de Oliveira</t>
@@ -919,7 +922,7 @@
         <v>1.5998329292E10</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>11</v>
@@ -940,7 +943,7 @@
         <v>45988.4735315625</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="11">
         <v>33.0</v>
@@ -949,7 +952,7 @@
         <v>1.5996661683E10</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>11</v>
@@ -970,7 +973,7 @@
         <v>45988.47454202546</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="11">
         <v>8.0</v>
@@ -979,7 +982,7 @@
         <v>1.5998329292E10</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>11</v>
@@ -1000,7 +1003,7 @@
         <v>45988.88085091436</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="8">
         <v>31.0</v>
@@ -1009,7 +1012,7 @@
         <v>1.5997383252E10</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>11</v>
@@ -1030,7 +1033,7 @@
         <v>45989.35557366898</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="14">
         <v>13.0</v>
@@ -1039,7 +1042,7 @@
         <v>1.5998073905E10</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>11</v>
@@ -1061,7 +1064,7 @@
         <v>45991.72189862268</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="8">
         <v>36.0</v>
@@ -1091,7 +1094,7 @@
         <v>45992.35183858796</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="14">
         <v>33.0</v>
@@ -1121,7 +1124,7 @@
         <v>46008.748270578704</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="8">
         <v>13.0</v>
@@ -1151,7 +1154,7 @@
         <v>46015.51542157408</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="8">
         <v>16.0</v>
@@ -1181,7 +1184,7 @@
         <v>46026.851575520835</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="11">
         <v>14.0</v>
@@ -1193,7 +1196,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>12</v>
@@ -1212,7 +1215,7 @@
         <v>46034.93480728009</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="14">
         <v>16.0</v>
@@ -1242,7 +1245,7 @@
         <v>46041.32586482639</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" s="8">
         <v>19.0</v>
@@ -1272,7 +1275,7 @@
         <v>46044.81511322917</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" s="8">
         <v>15.0</v>
@@ -1302,7 +1305,7 @@
         <v>46044.81827189815</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="8">
         <v>12.0</v>
@@ -1332,7 +1335,7 @@
         <v>46046.64678542824</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="14">
         <v>12.0</v>
@@ -1362,7 +1365,7 @@
         <v>46064.82448491898</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="8">
         <v>29.0</v>
@@ -1392,7 +1395,7 @@
         <v>46068.70991171296</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="14">
         <v>52.0</v>
@@ -1422,7 +1425,7 @@
         <v>46069.48487325231</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C23" s="14">
         <v>53.0</v>
@@ -1431,7 +1434,7 @@
         <v>1.9992764207E10</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>11</v>
@@ -1452,7 +1455,7 @@
         <v>46069.485649780094</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" s="14">
         <v>48.0</v>
@@ -1461,7 +1464,7 @@
         <v>1.9991540189E10</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>11</v>
@@ -1482,7 +1485,7 @@
         <v>46070.4851490625</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" s="14">
         <v>31.0</v>
@@ -1512,7 +1515,7 @@
         <v>46070.48898782408</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C26" s="14">
         <v>27.0</v>
@@ -1542,7 +1545,7 @@
         <v>46070.49287108796</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="8">
         <v>40.0</v>
@@ -1551,7 +1554,7 @@
         <v>1.9981865798E10</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>11</v>
@@ -1572,7 +1575,7 @@
         <v>46070.49458613426</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C28" s="8">
         <v>11.0</v>
@@ -1581,7 +1584,7 @@
         <v>1.9981865798E10</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>11</v>
@@ -1602,7 +1605,7 @@
         <v>46070.49686550926</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" s="8">
         <v>8.0</v>
@@ -1611,7 +1614,7 @@
         <v>1.9981865798E10</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>11</v>
@@ -1632,7 +1635,7 @@
         <v>46070.49971831018</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="8">
         <v>33.0</v>
@@ -1641,7 +1644,7 @@
         <v>1.9981865797E10</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>11</v>
@@ -1662,7 +1665,7 @@
         <v>46070.51280806713</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C31" s="8">
         <v>30.0</v>
@@ -1692,7 +1695,7 @@
         <v>46074.65327711806</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" s="14">
         <v>45.0</v>
@@ -1722,7 +1725,7 @@
         <v>46074.95314136574</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C33" s="14">
         <v>33.0</v>
@@ -1734,7 +1737,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>15</v>
@@ -1752,7 +1755,7 @@
         <v>46075.539279652774</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C34" s="8">
         <v>12.0</v>
@@ -1764,10 +1767,10 @@
         <v>10</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H34" s="6">
         <v>0.0</v>
@@ -1782,7 +1785,7 @@
         <v>46075.75095246528</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C35" s="14">
         <v>23.0</v>
@@ -1791,10 +1794,10 @@
         <v>1.998259793E10</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>15</v>
@@ -1812,7 +1815,7 @@
         <v>46075.75320802083</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C36" s="14">
         <v>20.0</v>
@@ -1821,10 +1824,10 @@
         <v>1.9981308647E10</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>15</v>
@@ -1842,7 +1845,7 @@
         <v>46078.29362975694</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C37" s="14">
         <v>34.0</v>
@@ -1851,10 +1854,10 @@
         <v>1.5996039339E10</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G37" s="14" t="s">
         <v>15</v>
@@ -1872,7 +1875,7 @@
         <v>46078.95354269676</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C38" s="8">
         <v>36.0</v>
@@ -1884,7 +1887,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>15</v>
@@ -1902,7 +1905,7 @@
         <v>46078.95630763889</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C39" s="8">
         <v>38.0</v>
@@ -1932,7 +1935,7 @@
         <v>46079.45182004629</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C40" s="8">
         <v>30.0</v>
@@ -1944,10 +1947,10 @@
         <v>10</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H40" s="6">
         <v>0.0</v>
@@ -1961,7 +1964,7 @@
         <v>46079.45345880787</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C41" s="8">
         <v>34.0</v>
@@ -1973,10 +1976,10 @@
         <v>10</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H41" s="6">
         <v>0.0</v>
@@ -1990,7 +1993,7 @@
         <v>46082.54593087963</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C42" s="8">
         <v>34.0</v>
@@ -2002,10 +2005,10 @@
         <v>10</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H42" s="6">
         <v>0.0</v>
@@ -2019,7 +2022,7 @@
         <v>46082.54697430556</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C43" s="8">
         <v>37.0</v>
@@ -2031,10 +2034,10 @@
         <v>10</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H43" s="6">
         <v>0.0</v>
@@ -2048,7 +2051,7 @@
         <v>46082.82621666667</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C44" s="8">
         <v>10.0</v>
@@ -2060,10 +2063,10 @@
         <v>10</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H44" s="6">
         <v>0.0</v>
@@ -2077,7 +2080,7 @@
         <v>46082.82685563657</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C45" s="8">
         <v>7.0</v>
@@ -2089,10 +2092,10 @@
         <v>10</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H45" s="6">
         <v>0.0</v>
@@ -2106,7 +2109,7 @@
         <v>46082.866330081015</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C46" s="8">
         <v>19.0</v>
@@ -2118,7 +2121,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>15</v>
@@ -2136,7 +2139,7 @@
         <v>46083.51295694444</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C47" s="14">
         <v>19.0</v>
@@ -2148,7 +2151,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>15</v>
@@ -2166,7 +2169,7 @@
         <v>46084.47416711805</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C48" s="11">
         <v>12.0</v>
@@ -2175,10 +2178,10 @@
         <v>1.5981381818E10</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G48" s="11" t="s">
         <v>15</v>
@@ -2196,7 +2199,7 @@
         <v>46088.44795631945</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C49" s="14">
         <v>61.0</v>
@@ -2205,10 +2208,10 @@
         <v>1.199997487E10</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G49" s="14" t="s">
         <v>15</v>
@@ -2226,7 +2229,7 @@
         <v>46088.44901105324</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C50" s="14">
         <v>64.0</v>
@@ -2235,10 +2238,10 @@
         <v>1.199997487E10</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G50" s="14" t="s">
         <v>15</v>
@@ -2256,7 +2259,7 @@
         <v>46091.45505960648</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C51" s="8">
         <v>37.0</v>
@@ -2265,13 +2268,13 @@
         <v>1.5981647628E10</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H51" s="6">
         <v>0.0</v>
@@ -2286,7 +2289,7 @@
         <v>46091.457525555554</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C52" s="8">
         <v>30.0</v>
@@ -2295,13 +2298,13 @@
         <v>1.599675357E10</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H52" s="6">
         <v>0.0</v>
@@ -2316,7 +2319,7 @@
         <v>46091.90208714121</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C53" s="8">
         <v>23.0</v>
@@ -2325,10 +2328,10 @@
         <v>1.9982012292E10</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>15</v>
@@ -2346,7 +2349,7 @@
         <v>46093.27018577546</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C54" s="14">
         <v>58.0</v>
@@ -2355,10 +2358,10 @@
         <v>1.5991416337E10</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G54" s="14" t="s">
         <v>15</v>
@@ -2376,7 +2379,7 @@
         <v>46093.27149944444</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C55" s="14">
         <v>58.0</v>
@@ -2385,10 +2388,10 @@
         <v>1.5988081595E10</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G55" s="14" t="s">
         <v>15</v>
@@ -2406,7 +2409,7 @@
         <v>46093.42218518518</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C56" s="8">
         <v>35.0</v>
@@ -2418,10 +2421,10 @@
         <v>10</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H56" s="6">
         <v>0.0</v>
@@ -2436,7 +2439,7 @@
         <v>46093.42287763889</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C57" s="8">
         <v>40.0</v>
@@ -2448,10 +2451,10 @@
         <v>10</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H57" s="6">
         <v>0.0</v>
@@ -2466,7 +2469,7 @@
         <v>46093.42378237269</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C58" s="8">
         <v>9.0</v>
@@ -2478,10 +2481,10 @@
         <v>10</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H58" s="6">
         <v>0.0</v>
@@ -2496,7 +2499,7 @@
         <v>46093.424697407405</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C59" s="8">
         <v>5.0</v>
@@ -2508,10 +2511,10 @@
         <v>10</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H59" s="6">
         <v>0.0</v>
@@ -2526,7 +2529,7 @@
         <v>46093.523896493054</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C60" s="8">
         <v>27.0</v>
@@ -2538,7 +2541,7 @@
         <v>10</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>15</v>
@@ -2556,7 +2559,7 @@
         <v>46093.70856616898</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C61" s="14">
         <v>19.0</v>
@@ -2568,7 +2571,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G61" s="14" t="s">
         <v>15</v>
@@ -2586,7 +2589,7 @@
         <v>46094.71026572917</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C62" s="8">
         <v>19.0</v>
@@ -2595,13 +2598,13 @@
         <v>1.1955200793E10</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H62" s="6">
         <v>0.0</v>
@@ -2616,7 +2619,7 @@
         <v>46095.34617701389</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C63" s="14">
         <v>37.0</v>
@@ -2625,13 +2628,13 @@
         <v>1.5997232525E10</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F63" s="14" t="s">
         <v>11</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H63" s="15">
         <v>200.0</v>
@@ -2652,7 +2655,7 @@
     <row r="66">
       <c r="A66" s="23"/>
       <c r="B66" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
@@ -3048,7 +3051,7 @@
   <sheetData>
     <row r="4">
       <c r="C4" s="27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" s="21">
         <f>SUM('Respostas ao formulário 1'!H2:H67)</f>
@@ -3059,7 +3062,7 @@
         <v>6748</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
@@ -3068,7 +3071,7 @@
     </row>
     <row r="6">
       <c r="C6" s="27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" s="22">
         <f>300+100</f>
@@ -3086,7 +3089,7 @@
     </row>
     <row r="9">
       <c r="C9" s="27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" s="21">
         <f>D4+D6</f>

--- a/dados/123.xlsx
+++ b/dados/123.xlsx
@@ -7,14 +7,14 @@
     <sheet state="visible" name="Controle" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respostas ao formulário 1'!$A$1:$I$63</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respostas ao formulário 1'!$A$1:$I$64</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="99">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -287,6 +287,15 @@
   </si>
   <si>
     <t>Eric Tiago Machado Vieira</t>
+  </si>
+  <si>
+    <t>Ana isabeli Reis Domingues</t>
+  </si>
+  <si>
+    <t>+55 15 99622-2210</t>
+  </si>
+  <si>
+    <t>Igreja Presbiteriana do Brasil Pilar do Sul</t>
   </si>
   <si>
     <t>Daniele Lopes Ferreira - Pago dia 25/02 - é inscrição da Pamela</t>
@@ -369,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -431,6 +440,9 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -531,8 +543,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I63" displayName="Form_Responses" name="Form_Responses" id="1">
-  <autoFilter ref="$A$1:$I$63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I64" displayName="Form_Responses" name="Form_Responses" id="1">
+  <autoFilter ref="$A$1:$I$64"/>
   <tableColumns count="9">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="Nome completo" id="2"/>
@@ -2130,7 +2142,7 @@
         <v>0.0</v>
       </c>
       <c r="I46" s="19">
-        <f t="shared" ref="I46:I63" si="3">200-H46</f>
+        <f t="shared" ref="I46:I64" si="3">200-H46</f>
         <v>200</v>
       </c>
     </row>
@@ -2644,395 +2656,422 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="A64" s="9">
+        <v>46095.451927685186</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="8">
+        <v>15.0</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="21">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="65">
       <c r="H65" s="22"/>
-      <c r="I65" s="21"/>
+      <c r="I65" s="22"/>
     </row>
     <row r="66">
-      <c r="A66" s="23"/>
-      <c r="B66" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
-      <c r="H66" s="25">
+      <c r="H66" s="23"/>
+      <c r="I66" s="22"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="24"/>
+      <c r="B67" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="26">
         <v>200.0</v>
       </c>
-      <c r="I66" s="26">
-        <f>200-H66</f>
+      <c r="I67" s="27">
+        <f>200-H67</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67">
-      <c r="H67" s="21"/>
-      <c r="I67" s="21"/>
-    </row>
     <row r="68">
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-    </row>
-    <row r="75">
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+    </row>
+    <row r="69">
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
     </row>
     <row r="76">
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="22"/>
     </row>
     <row r="77">
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
     </row>
     <row r="78">
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
     </row>
     <row r="79">
-      <c r="H79" s="21"/>
-      <c r="I79" s="21"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
     </row>
     <row r="80">
-      <c r="H80" s="21"/>
-      <c r="I80" s="21"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
     </row>
     <row r="81">
-      <c r="H81" s="21"/>
-      <c r="I81" s="21"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="22"/>
     </row>
     <row r="82">
-      <c r="H82" s="21"/>
-      <c r="I82" s="21"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="22"/>
     </row>
     <row r="83">
-      <c r="H83" s="21"/>
-      <c r="I83" s="21"/>
+      <c r="H83" s="22"/>
+      <c r="I83" s="22"/>
     </row>
     <row r="84">
-      <c r="H84" s="21"/>
-      <c r="I84" s="21"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="22"/>
     </row>
     <row r="85">
-      <c r="H85" s="21"/>
-      <c r="I85" s="21"/>
+      <c r="H85" s="22"/>
+      <c r="I85" s="22"/>
     </row>
     <row r="86">
-      <c r="H86" s="21"/>
-      <c r="I86" s="21"/>
+      <c r="H86" s="22"/>
+      <c r="I86" s="22"/>
     </row>
     <row r="87">
-      <c r="H87" s="21"/>
-      <c r="I87" s="21"/>
+      <c r="H87" s="22"/>
+      <c r="I87" s="22"/>
     </row>
     <row r="88">
-      <c r="H88" s="21"/>
-      <c r="I88" s="21"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="22"/>
     </row>
     <row r="89">
-      <c r="H89" s="21"/>
-      <c r="I89" s="21"/>
+      <c r="H89" s="22"/>
+      <c r="I89" s="22"/>
     </row>
     <row r="90">
-      <c r="H90" s="21"/>
-      <c r="I90" s="21"/>
+      <c r="H90" s="22"/>
+      <c r="I90" s="22"/>
     </row>
     <row r="91">
-      <c r="H91" s="21"/>
-      <c r="I91" s="21"/>
+      <c r="H91" s="22"/>
+      <c r="I91" s="22"/>
     </row>
     <row r="92">
-      <c r="H92" s="21"/>
-      <c r="I92" s="21"/>
+      <c r="H92" s="22"/>
+      <c r="I92" s="22"/>
     </row>
     <row r="93">
-      <c r="H93" s="21"/>
-      <c r="I93" s="21"/>
+      <c r="H93" s="22"/>
+      <c r="I93" s="22"/>
     </row>
     <row r="94">
-      <c r="H94" s="21"/>
-      <c r="I94" s="21"/>
+      <c r="H94" s="22"/>
+      <c r="I94" s="22"/>
     </row>
     <row r="95">
-      <c r="H95" s="21"/>
-      <c r="I95" s="21"/>
+      <c r="H95" s="22"/>
+      <c r="I95" s="22"/>
     </row>
     <row r="96">
-      <c r="H96" s="21"/>
-      <c r="I96" s="21"/>
+      <c r="H96" s="22"/>
+      <c r="I96" s="22"/>
     </row>
     <row r="97">
-      <c r="H97" s="21"/>
-      <c r="I97" s="21"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="22"/>
     </row>
     <row r="98">
-      <c r="H98" s="21"/>
-      <c r="I98" s="21"/>
+      <c r="H98" s="22"/>
+      <c r="I98" s="22"/>
     </row>
     <row r="99">
-      <c r="H99" s="21"/>
-      <c r="I99" s="21"/>
+      <c r="H99" s="22"/>
+      <c r="I99" s="22"/>
     </row>
     <row r="100">
-      <c r="H100" s="21"/>
-      <c r="I100" s="21"/>
+      <c r="H100" s="22"/>
+      <c r="I100" s="22"/>
     </row>
     <row r="101">
-      <c r="H101" s="21"/>
-      <c r="I101" s="21"/>
+      <c r="H101" s="22"/>
+      <c r="I101" s="22"/>
     </row>
     <row r="102">
-      <c r="H102" s="21"/>
-      <c r="I102" s="21"/>
+      <c r="H102" s="22"/>
+      <c r="I102" s="22"/>
     </row>
     <row r="103">
-      <c r="H103" s="21"/>
-      <c r="I103" s="21"/>
+      <c r="H103" s="22"/>
+      <c r="I103" s="22"/>
     </row>
     <row r="104">
-      <c r="H104" s="21"/>
-      <c r="I104" s="21"/>
+      <c r="H104" s="22"/>
+      <c r="I104" s="22"/>
     </row>
     <row r="105">
-      <c r="H105" s="21"/>
-      <c r="I105" s="21"/>
+      <c r="H105" s="22"/>
+      <c r="I105" s="22"/>
     </row>
     <row r="106">
-      <c r="H106" s="21"/>
-      <c r="I106" s="21"/>
+      <c r="H106" s="22"/>
+      <c r="I106" s="22"/>
     </row>
     <row r="107">
-      <c r="H107" s="21"/>
-      <c r="I107" s="21"/>
+      <c r="H107" s="22"/>
+      <c r="I107" s="22"/>
     </row>
     <row r="108">
-      <c r="H108" s="21"/>
-      <c r="I108" s="21"/>
+      <c r="H108" s="22"/>
+      <c r="I108" s="22"/>
     </row>
     <row r="109">
-      <c r="H109" s="21"/>
-      <c r="I109" s="21"/>
+      <c r="H109" s="22"/>
+      <c r="I109" s="22"/>
     </row>
     <row r="110">
-      <c r="H110" s="21"/>
-      <c r="I110" s="21"/>
+      <c r="H110" s="22"/>
+      <c r="I110" s="22"/>
     </row>
     <row r="111">
-      <c r="H111" s="21"/>
-      <c r="I111" s="21"/>
+      <c r="H111" s="22"/>
+      <c r="I111" s="22"/>
     </row>
     <row r="112">
-      <c r="H112" s="21"/>
-      <c r="I112" s="21"/>
+      <c r="H112" s="22"/>
+      <c r="I112" s="22"/>
     </row>
     <row r="113">
-      <c r="H113" s="21"/>
-      <c r="I113" s="21"/>
+      <c r="H113" s="22"/>
+      <c r="I113" s="22"/>
     </row>
     <row r="114">
-      <c r="H114" s="21"/>
-      <c r="I114" s="21"/>
+      <c r="H114" s="22"/>
+      <c r="I114" s="22"/>
     </row>
     <row r="115">
-      <c r="H115" s="21"/>
-      <c r="I115" s="21"/>
+      <c r="H115" s="22"/>
+      <c r="I115" s="22"/>
     </row>
     <row r="116">
-      <c r="H116" s="21"/>
-      <c r="I116" s="21"/>
+      <c r="H116" s="22"/>
+      <c r="I116" s="22"/>
     </row>
     <row r="117">
-      <c r="H117" s="21"/>
-      <c r="I117" s="21"/>
+      <c r="H117" s="22"/>
+      <c r="I117" s="22"/>
     </row>
     <row r="118">
-      <c r="H118" s="21"/>
-      <c r="I118" s="21"/>
+      <c r="H118" s="22"/>
+      <c r="I118" s="22"/>
     </row>
     <row r="119">
-      <c r="H119" s="21"/>
-      <c r="I119" s="21"/>
+      <c r="H119" s="22"/>
+      <c r="I119" s="22"/>
     </row>
     <row r="120">
-      <c r="H120" s="21"/>
-      <c r="I120" s="21"/>
+      <c r="H120" s="22"/>
+      <c r="I120" s="22"/>
     </row>
     <row r="121">
-      <c r="H121" s="21"/>
-      <c r="I121" s="21"/>
+      <c r="H121" s="22"/>
+      <c r="I121" s="22"/>
     </row>
     <row r="122">
-      <c r="H122" s="21"/>
-      <c r="I122" s="21"/>
+      <c r="H122" s="22"/>
+      <c r="I122" s="22"/>
     </row>
     <row r="123">
-      <c r="H123" s="21"/>
-      <c r="I123" s="21"/>
+      <c r="H123" s="22"/>
+      <c r="I123" s="22"/>
     </row>
     <row r="124">
-      <c r="H124" s="21"/>
-      <c r="I124" s="21"/>
+      <c r="H124" s="22"/>
+      <c r="I124" s="22"/>
     </row>
     <row r="125">
-      <c r="H125" s="21"/>
-      <c r="I125" s="21"/>
+      <c r="H125" s="22"/>
+      <c r="I125" s="22"/>
     </row>
     <row r="126">
-      <c r="H126" s="21"/>
-      <c r="I126" s="21"/>
+      <c r="H126" s="22"/>
+      <c r="I126" s="22"/>
     </row>
     <row r="127">
-      <c r="H127" s="21"/>
-      <c r="I127" s="21"/>
+      <c r="H127" s="22"/>
+      <c r="I127" s="22"/>
     </row>
     <row r="128">
-      <c r="H128" s="21"/>
-      <c r="I128" s="21"/>
+      <c r="H128" s="22"/>
+      <c r="I128" s="22"/>
     </row>
     <row r="129">
-      <c r="H129" s="21"/>
-      <c r="I129" s="21"/>
+      <c r="H129" s="22"/>
+      <c r="I129" s="22"/>
     </row>
     <row r="130">
-      <c r="H130" s="21"/>
-      <c r="I130" s="21"/>
+      <c r="H130" s="22"/>
+      <c r="I130" s="22"/>
     </row>
     <row r="131">
-      <c r="H131" s="21"/>
-      <c r="I131" s="21"/>
+      <c r="H131" s="22"/>
+      <c r="I131" s="22"/>
     </row>
     <row r="132">
-      <c r="H132" s="21"/>
-      <c r="I132" s="21"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22"/>
     </row>
     <row r="133">
-      <c r="H133" s="21"/>
-      <c r="I133" s="21"/>
+      <c r="H133" s="22"/>
+      <c r="I133" s="22"/>
     </row>
     <row r="134">
-      <c r="H134" s="21"/>
-      <c r="I134" s="21"/>
+      <c r="H134" s="22"/>
+      <c r="I134" s="22"/>
     </row>
     <row r="135">
-      <c r="H135" s="21"/>
-      <c r="I135" s="21"/>
+      <c r="H135" s="22"/>
+      <c r="I135" s="22"/>
     </row>
     <row r="136">
-      <c r="H136" s="21"/>
-      <c r="I136" s="21"/>
+      <c r="H136" s="22"/>
+      <c r="I136" s="22"/>
     </row>
     <row r="137">
-      <c r="H137" s="21"/>
-      <c r="I137" s="21"/>
+      <c r="H137" s="22"/>
+      <c r="I137" s="22"/>
     </row>
     <row r="138">
-      <c r="H138" s="21"/>
-      <c r="I138" s="21"/>
+      <c r="H138" s="22"/>
+      <c r="I138" s="22"/>
     </row>
     <row r="139">
-      <c r="H139" s="21"/>
-      <c r="I139" s="21"/>
+      <c r="H139" s="22"/>
+      <c r="I139" s="22"/>
     </row>
     <row r="140">
-      <c r="H140" s="21"/>
-      <c r="I140" s="21"/>
+      <c r="H140" s="22"/>
+      <c r="I140" s="22"/>
     </row>
     <row r="141">
-      <c r="H141" s="21"/>
-      <c r="I141" s="21"/>
+      <c r="H141" s="22"/>
+      <c r="I141" s="22"/>
     </row>
     <row r="142">
-      <c r="H142" s="21"/>
-      <c r="I142" s="21"/>
+      <c r="H142" s="22"/>
+      <c r="I142" s="22"/>
     </row>
     <row r="143">
-      <c r="H143" s="21"/>
-      <c r="I143" s="21"/>
+      <c r="H143" s="22"/>
+      <c r="I143" s="22"/>
     </row>
     <row r="144">
-      <c r="H144" s="21"/>
-      <c r="I144" s="21"/>
+      <c r="H144" s="22"/>
+      <c r="I144" s="22"/>
     </row>
     <row r="145">
-      <c r="H145" s="21"/>
-      <c r="I145" s="21"/>
+      <c r="H145" s="22"/>
+      <c r="I145" s="22"/>
     </row>
     <row r="146">
-      <c r="H146" s="21"/>
-      <c r="I146" s="21"/>
+      <c r="H146" s="22"/>
+      <c r="I146" s="22"/>
     </row>
     <row r="147">
-      <c r="H147" s="21"/>
-      <c r="I147" s="21"/>
+      <c r="H147" s="22"/>
+      <c r="I147" s="22"/>
     </row>
     <row r="148">
-      <c r="H148" s="21"/>
-      <c r="I148" s="21"/>
+      <c r="H148" s="22"/>
+      <c r="I148" s="22"/>
     </row>
     <row r="149">
-      <c r="H149" s="21"/>
-      <c r="I149" s="21"/>
+      <c r="H149" s="22"/>
+      <c r="I149" s="22"/>
     </row>
     <row r="150">
-      <c r="H150" s="21"/>
-      <c r="I150" s="21"/>
+      <c r="H150" s="22"/>
+      <c r="I150" s="22"/>
     </row>
     <row r="151">
-      <c r="H151" s="21"/>
-      <c r="I151" s="21"/>
+      <c r="H151" s="22"/>
+      <c r="I151" s="22"/>
     </row>
     <row r="152">
-      <c r="H152" s="21"/>
-      <c r="I152" s="21"/>
+      <c r="H152" s="22"/>
+      <c r="I152" s="22"/>
     </row>
     <row r="153">
-      <c r="H153" s="21"/>
-      <c r="I153" s="21"/>
+      <c r="H153" s="22"/>
+      <c r="I153" s="22"/>
     </row>
     <row r="154">
-      <c r="H154" s="21"/>
-      <c r="I154" s="21"/>
+      <c r="H154" s="22"/>
+      <c r="I154" s="22"/>
     </row>
     <row r="155">
-      <c r="H155" s="21"/>
-      <c r="I155" s="21"/>
+      <c r="H155" s="22"/>
+      <c r="I155" s="22"/>
     </row>
     <row r="156">
-      <c r="H156" s="21"/>
-      <c r="I156" s="21"/>
+      <c r="H156" s="22"/>
+      <c r="I156" s="22"/>
     </row>
     <row r="157">
-      <c r="H157" s="21"/>
-      <c r="I157" s="21"/>
+      <c r="H157" s="22"/>
+      <c r="I157" s="22"/>
     </row>
     <row r="158">
-      <c r="H158" s="21"/>
-      <c r="I158" s="21"/>
+      <c r="H158" s="22"/>
+      <c r="I158" s="22"/>
     </row>
     <row r="159">
-      <c r="H159" s="21"/>
-      <c r="I159" s="21"/>
+      <c r="H159" s="22"/>
+      <c r="I159" s="22"/>
     </row>
     <row r="160">
-      <c r="H160" s="21"/>
-      <c r="I160" s="21"/>
+      <c r="H160" s="22"/>
+      <c r="I160" s="22"/>
     </row>
     <row r="161">
-      <c r="H161" s="21"/>
-      <c r="I161" s="21"/>
+      <c r="H161" s="22"/>
+      <c r="I161" s="22"/>
     </row>
     <row r="162">
-      <c r="H162" s="21"/>
-      <c r="I162" s="21"/>
+      <c r="H162" s="22"/>
+      <c r="I162" s="22"/>
     </row>
     <row r="163">
-      <c r="H163" s="21"/>
-      <c r="I163" s="21"/>
+      <c r="H163" s="22"/>
+      <c r="I163" s="22"/>
+    </row>
+    <row r="164">
+      <c r="H164" s="22"/>
+      <c r="I164" s="22"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -3050,52 +3089,52 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="4">
-      <c r="C4" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="21">
-        <f>SUM('Respostas ao formulário 1'!H2:H67)</f>
+      <c r="C4" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="22">
+        <f>SUM('Respostas ao formulário 1'!H2:H68)</f>
         <v>5082</v>
       </c>
-      <c r="E4" s="21">
-        <f>SUM('Respostas ao formulário 1'!I2:I67)</f>
-        <v>6748</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>93</v>
+      <c r="E4" s="22">
+        <f>SUM('Respostas ao formulário 1'!I2:I68)</f>
+        <v>6948</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
     </row>
     <row r="6">
-      <c r="C6" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="22">
+      <c r="C6" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="23">
         <f>300+100</f>
         <v>400</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="22"/>
     </row>
     <row r="7">
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="8">
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
     </row>
     <row r="9">
-      <c r="C9" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="21">
+      <c r="C9" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="22">
         <f>D4+D6</f>
         <v>5482</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="22"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
